--- a/USUARIOS_CRM.xlsx
+++ b/USUARIOS_CRM.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuarios" sheetId="1" r:id="Rebbe8f8fb7834e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consulta Supabase" sheetId="2" r:id="R6f414e038c5046d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Usuarios" sheetId="1" r:id="R34d8f39ccc4b4ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consulta Supabase" sheetId="2" r:id="Re9572bc9762648d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -102,34 +102,12 @@
   <x:borders count="8">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -330,9 +308,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -519,12 +497,12 @@
         <x:v>Supabase Authentication y perfil del CRM</x:v>
       </x:c>
       <x:c r="H5" s="40" t="str">
-        <x:v>Cuenta confirmada en la información compartida. Ejecutar SQL/listar-usuarios.sql para obtener la lista real completa de Supabase.</x:v>
+        <x:v>Cuenta confirmada en la información compartida. Para consultar la lista real completa de Supabase, usa SQL_MAESTRO_CRM.sql o SQL_MAESTRO_2_ACTUALIZACION_V144.sql.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="38" customHeight="1">
       <x:c r="A7" s="54" t="str">
-        <x:v>IMPORTANTE: para mantener esta lista actualizada, ejecuta el archivo SQL/listar-usuarios.sql en Supabase.</x:v>
+        <x:v>IMPORTANTE: para mantener esta lista actualizada, usa las consultas consolidadas de SQL_MAESTRO_CRM.sql o SQL_MAESTRO_2_ACTUALIZACION_V144.sql en Supabase.</x:v>
       </x:c>
       <x:c r="B7" s="54"/>
       <x:c r="C7" s="54"/>
@@ -573,7 +551,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="65" t="str">
-        <x:v>Abre Supabase → SQL Editor y ejecuta el archivo SQL/listar-usuarios.sql incluido en el CRM. La consulta devuelve correo, nombre, puesto, departamento, rol, estado, confirmación, último acceso y fecha de alta.</x:v>
+        <x:v>Abre Supabase → SQL Editor y usa SQL_MAESTRO_CRM.sql para una instalación completa o SQL_MAESTRO_2_ACTUALIZACION_V144.sql si ya tienes V143. Después ejecuta la consulta indicada abajo para listar los usuarios.</x:v>
       </x:c>
       <x:c r="B4" s="65"/>
       <x:c r="C4" s="65"/>
@@ -590,8 +568,12 @@
       <x:c r="F5" s="65"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="65"/>
-      <x:c r="B6" s="65"/>
+      <x:c r="A6" s="65" t="str">
+        <x:v>Consulta</x:v>
+      </x:c>
+      <x:c r="B6" s="65" t="str">
+        <x:v>select * from public.crm_listar_usuarios_v144();</x:v>
+      </x:c>
       <x:c r="C6" s="65"/>
       <x:c r="D6" s="65"/>
       <x:c r="E6" s="65"/>
@@ -602,7 +584,7 @@
         <x:v>Archivo</x:v>
       </x:c>
       <x:c r="B8" s="70" t="str">
-        <x:v>SQL/listar-usuarios.sql</x:v>
+        <x:v>SQL_MAESTRO_CRM.sql / SQL_MAESTRO_2_ACTUALIZACION_V144.sql</x:v>
       </x:c>
       <x:c r="C8" s="70"/>
       <x:c r="D8" s="70"/>
